--- a/custom ordered parts/harness/harness wiring.xlsx
+++ b/custom ordered parts/harness/harness wiring.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\3d printing\stormwalker\harness\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\3d printing\stormwalker\custom ordered parts\harness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357861BB-5E9B-4933-9B38-D1B2FFA70601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E9471E-2A46-4C3D-8380-6BC03551E6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29772" yWindow="5580" windowWidth="14748" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4848" yWindow="4668" windowWidth="34560" windowHeight="18852" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="24pin" sheetId="1" r:id="rId1"/>
     <sheet name="20pin" sheetId="3" r:id="rId2"/>
+    <sheet name="Sum" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
   <si>
     <t>name</t>
   </si>
@@ -46,9 +47,6 @@
     <t>pin</t>
   </si>
   <si>
-    <t>EM1</t>
-  </si>
-  <si>
     <t>XHP4</t>
   </si>
   <si>
@@ -67,9 +65,6 @@
     <t>XR1</t>
   </si>
   <si>
-    <t>XEND1</t>
-  </si>
-  <si>
     <t>XHP3</t>
   </si>
   <si>
@@ -164,10 +159,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>motor slot 8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PD14</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -192,14 +183,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>motor slot 6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>motor slot 7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TMC5160Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -225,6 +208,58 @@
   </si>
   <si>
     <t>PD11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stepper slot 8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stepper slot 6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stepper slot 7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Side A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Side B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gauge</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qty.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Molex 3.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bare Wire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XH2.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XEND</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -232,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +283,19 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <scheme val="minor"/>
     </font>
@@ -326,7 +374,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -339,17 +387,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -417,13 +477,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:colOff>60078</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1438</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>722405</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>266866</xdr:rowOff>
     </xdr:to>
@@ -459,8 +519,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="4295775" y="3162300"/>
-          <a:ext cx="666750" cy="1190625"/>
+          <a:off x="3840770" y="3125665"/>
+          <a:ext cx="662327" cy="1179801"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -472,13 +532,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>78440</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3342</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>720517</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>276349</xdr:rowOff>
     </xdr:to>
@@ -514,8 +574,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="4314825" y="5676900"/>
-          <a:ext cx="657225" cy="885825"/>
+          <a:off x="3870511" y="5666815"/>
+          <a:ext cx="642077" cy="884828"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -528,14 +588,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>83484</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>287214</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>719507</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>48279</xdr:rowOff>
+      <xdr:rowOff>24831</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -569,8 +629,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="4283710" y="8486775"/>
-          <a:ext cx="636270" cy="676910"/>
+          <a:off x="3864176" y="8364414"/>
+          <a:ext cx="636023" cy="669602"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -584,13 +644,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>295275</xdr:rowOff>
+      <xdr:rowOff>289413</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>721748</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>29229</xdr:rowOff>
+      <xdr:rowOff>23367</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -624,8 +684,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="4286250" y="9096375"/>
-          <a:ext cx="635635" cy="676910"/>
+          <a:off x="3866417" y="8987936"/>
+          <a:ext cx="636023" cy="665939"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -639,13 +699,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>295275</xdr:rowOff>
+      <xdr:rowOff>289413</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>721748</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>29229</xdr:rowOff>
+      <xdr:rowOff>23367</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -679,8 +739,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="4286250" y="9725025"/>
-          <a:ext cx="635635" cy="676910"/>
+          <a:off x="3866417" y="9609259"/>
+          <a:ext cx="636023" cy="665939"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -694,13 +754,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>74545</xdr:rowOff>
+      <xdr:rowOff>128510</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>742950</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>150746</xdr:rowOff>
+      <xdr:rowOff>96780</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -724,14 +784,12 @@
           </a:extLst>
         </a:blip>
         <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1331595"/>
-          <a:ext cx="4943475" cy="1333500"/>
+          <a:off x="0" y="1391253"/>
+          <a:ext cx="4531179" cy="1231013"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -755,13 +813,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>90767</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>293034</xdr:rowOff>
+      <xdr:rowOff>287172</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>726790</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>26988</xdr:rowOff>
+      <xdr:rowOff>21126</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -795,8 +853,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="3882838" y="10647269"/>
-          <a:ext cx="636023" cy="675248"/>
+          <a:off x="3871459" y="10539003"/>
+          <a:ext cx="636023" cy="665938"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -969,13 +1027,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>58160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1905</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>18040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -999,14 +1057,12 @@
           </a:extLst>
         </a:blip>
         <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1257300"/>
-          <a:ext cx="4133850" cy="1333500"/>
+          <a:off x="0" y="1320903"/>
+          <a:ext cx="3790134" cy="1222623"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1527,91 +1583,91 @@
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="6">
-        <v>22</v>
+      <c r="C11" s="5">
+        <v>26</v>
       </c>
       <c r="D11" s="2">
         <v>14</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="G11" s="6" t="s">
-        <v>41</v>
+      <c r="G11" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="2">
         <v>13</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="G12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="2">
         <v>2</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="G13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="G14" s="6"/>
+      <c r="E14" s="4"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>22</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="2">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>7</v>
+      <c r="B17" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C17" s="3">
         <v>22</v>
@@ -1620,254 +1676,254 @@
         <v>5</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="5"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
       <c r="D18" s="2">
         <v>6</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" s="3"/>
-      <c r="G19" s="6" t="s">
-        <v>44</v>
+      <c r="G19" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="4"/>
-      <c r="G20" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
       <c r="C21" s="2">
         <v>26</v>
       </c>
       <c r="D21" s="2">
         <v>7</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="G21" s="6"/>
+      <c r="E21" s="4"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="6">
+      <c r="A22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="5">
         <v>22</v>
       </c>
       <c r="D22" s="2">
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="23" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="2">
         <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
       <c r="D24" s="2">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="2">
         <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="5">
         <v>20</v>
-      </c>
-      <c r="C26" s="6">
-        <v>22</v>
       </c>
       <c r="D26" s="2">
         <v>12</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="27" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="2">
         <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G27" s="7"/>
-      <c r="H27" s="6"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="6">
+      <c r="A28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="5">
         <v>26</v>
       </c>
       <c r="D28" s="2">
         <v>15</v>
       </c>
       <c r="E28" s="3"/>
-      <c r="G28" s="6" t="s">
-        <v>45</v>
+      <c r="G28" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
       <c r="D29" s="2">
         <v>16</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="G29" s="6"/>
+      <c r="E29" s="4"/>
+      <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="A30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="5">
         <v>26</v>
       </c>
       <c r="D30" s="2">
         <v>17</v>
       </c>
       <c r="E30" s="3"/>
-      <c r="G30" s="6" t="s">
-        <v>46</v>
+      <c r="G30" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
       <c r="D31" s="2">
         <v>18</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="G31" s="6"/>
+      <c r="E31" s="4"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="6">
+      <c r="B32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="5">
         <v>26</v>
       </c>
       <c r="D32" s="2">
         <v>19</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="G32" s="6" t="s">
-        <v>47</v>
+      <c r="G32" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
       <c r="D33" s="2">
         <v>20</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="G33" s="6"/>
+      <c r="E33" s="4"/>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" ht="24.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2">
         <v>22</v>
@@ -1876,39 +1932,39 @@
         <v>21</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G34" s="2"/>
     </row>
     <row r="35" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A35" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>39</v>
+      <c r="A35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E35" s="3"/>
-      <c r="G35" s="6" t="s">
-        <v>40</v>
+      <c r="G35" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
       <c r="C36" s="2">
         <v>26</v>
       </c>
       <c r="D36" s="2">
         <v>23</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="G36" s="6"/>
+      <c r="E36" s="4"/>
+      <c r="G36" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="46">
@@ -1998,43 +2054,43 @@
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>7</v>
+      <c r="A11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C11" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>52</v>
+        <v>7</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="5"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="2">
         <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>22</v>
+      <c r="A13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <v>26</v>
@@ -2043,303 +2099,303 @@
         <v>3</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="G13" s="6" t="s">
-        <v>53</v>
+      <c r="G13" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="5"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="2">
         <v>4</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="G14" s="6"/>
+      <c r="E14" s="4"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="A15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5">
         <v>26</v>
       </c>
       <c r="D15" s="2">
         <v>15</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="G15" s="6" t="s">
-        <v>48</v>
+      <c r="G15" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="2">
         <v>16</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="G16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="2">
         <v>6</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="G17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="2">
         <v>5</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="G18" s="6"/>
+      <c r="E18" s="4"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="6">
-        <v>22</v>
+      <c r="A19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>20</v>
       </c>
       <c r="D19" s="2">
         <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>51</v>
+        <v>13</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
       <c r="D20" s="2">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="2">
         <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="2">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A23" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>12</v>
+      <c r="A23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E23" s="3"/>
-      <c r="G23" s="6" t="s">
-        <v>54</v>
+      <c r="G23" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
       <c r="C24" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="4"/>
-      <c r="G24" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
       <c r="C25" s="2">
         <v>26</v>
       </c>
       <c r="D25" s="2">
         <v>11</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="G25" s="6"/>
+      <c r="E25" s="4"/>
+      <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A26" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>12</v>
+      <c r="A26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" s="3"/>
-      <c r="G26" s="6" t="s">
-        <v>55</v>
+      <c r="G26" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
       <c r="C27" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="G27" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
       <c r="C28" s="2">
         <v>26</v>
       </c>
       <c r="D28" s="2">
         <v>12</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="G28" s="6"/>
+      <c r="E28" s="4"/>
+      <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>12</v>
+      <c r="A29" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E29" s="3"/>
-      <c r="G29" s="6" t="s">
-        <v>56</v>
+      <c r="G29" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
       <c r="C30" s="2">
         <v>26</v>
       </c>
       <c r="D30" s="2">
         <v>14</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="G30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
       <c r="C31" s="2">
         <v>26</v>
       </c>
       <c r="D31" s="2">
         <v>13</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="G31" s="6"/>
+      <c r="E31" s="4"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="6">
+      <c r="A32" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="5">
         <v>26</v>
       </c>
       <c r="D32" s="2">
         <v>20</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="G32" s="6" t="s">
-        <v>49</v>
+      <c r="G32" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
       <c r="D33" s="2">
         <v>19</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="G33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
       <c r="D34" s="2">
         <v>18</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="G34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
       <c r="D35" s="2">
         <v>17</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="G35" s="6"/>
+      <c r="E35" s="4"/>
+      <c r="G35" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -2355,14 +2411,15 @@
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="B19:B22"/>
     <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B32:B35"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A18"/>
@@ -2373,7 +2430,6 @@
     <mergeCell ref="C15:C18"/>
     <mergeCell ref="C19:C22"/>
     <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="E15:E18"/>
     <mergeCell ref="E23:E25"/>
@@ -2384,4 +2440,88 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B8986E-5FD7-436E-B541-EE6C55166B40}">
+  <dimension ref="B3:F6"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="8"/>
+    <col min="2" max="2" width="5.77734375" style="8" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6">
+      <c r="B3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="10">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10">
+        <v>8</v>
+      </c>
+      <c r="D4" s="10">
+        <v>20</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="10">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10">
+        <v>9</v>
+      </c>
+      <c r="D5" s="10">
+        <v>22</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="10">
+        <v>3</v>
+      </c>
+      <c r="C6" s="10">
+        <v>26</v>
+      </c>
+      <c r="D6" s="10">
+        <v>26</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>